--- a/Στατιστικα Αγωνα - 29η Αγωνιστικη - Νικη Μεσημεριου.xlsx
+++ b/Στατιστικα Αγωνα - 29η Αγωνιστικη - Νικη Μεσημεριου.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://campeongaming-my.sharepoint.com/personal/dimitris_chatziliadis_campeongaming_com/Documents/Επιφάνεια εργασίας/mpam/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://campeongaming-my.sharepoint.com/personal/dimitris_chatziliadis_campeongaming_com/Documents/Επιφάνεια εργασίας/mpam/Stats/Season 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1145" documentId="8_{BB149310-9C70-4F0D-AF38-12983800A995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6DE8988-2D79-4E29-8744-6ECB9A0C352B}"/>
+  <xr:revisionPtr revIDLastSave="1146" documentId="8_{BB149310-9C70-4F0D-AF38-12983800A995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E522EA7-508A-4088-851F-B980D4D05FFC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -493,9 +493,6 @@
     <t>ΔΑΡΑΗΣ</t>
   </si>
   <si>
-    <t>ΜΑΡΝΕΡΣ</t>
-  </si>
-  <si>
     <t>ΚΑΚΑΤΑΤΣΙΟΣ</t>
   </si>
   <si>
@@ -506,6 +503,9 @@
   </si>
   <si>
     <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAVsAAADfCAYAAABYmXCXAAAAAXNSR0IArs4c6QAAAARnQU1BAACxjwv8YQUAAAAJcEhZcwAAEnQAABJ0Ad5mH3gAACcVSURBVHhe7d15fFTV3T/wz52Z7CSBbJAEwhbCLksiCIoCouASUawoKvK44fKz9lGeauvTPtpq61ZrtUo1KiBaARE3QKm2IrIaAoisCWtYsidk32fu7487mbn3TCaZLHMzy+f9euVF5ntOSAh3PnPn3HPOlVJTU2VkLYa0Nx9E3kCeGM/jlbyGPDEeSMuA1BK2SMsQ+xB5Jh6v5E2sx6tBrBMRUfdj2BIR6YBhS0SkA4YtEZEOGLZERDpg2BIR6YBhS0SkA4YtEZEOGLZERDpg2BIR6YBhS0RuV5k4CWem/RanZj6H4pHzxGa/wLAlIrcqGrsAx65diuKRN6MseQ7OTHsKx2f/Vezm8xi2ROQ2TSHRODtlCSRLo60myWZUDLwcJSNv0vT1dQxbInKb2tiRgATIxkBbTZaMAIDqfhNUPX0fw5aI3MbQVAvIYlVhaKwWSz6NYUtEbhOevxdBFWcByV4zmJUhhT6nN9uLfoBhS0RuNfi7/0VQ+TnbY4sxEAN2/AXh53dr+vk6hi0RuVVY8WGMWXMjUjY8gORNj+GiD2cj7uBqsZvPY9gSkS7C8/Yg8sxWBNSWik1+gWFLRKQDhi0RkQ4YtkREOmDYEhHpgGFLRKQDhi0RkQ4YtkREOmDYEhHpgGFLRKQDhi0RkQ4YtkREOmDYEhHpgGFLRKQDhi0RkQ4YtkREOmDYEhHpgGFLRKQDhi0RkQ4YtkREOmDYEhHpgGFLRKQDhi0RkQ4YtkREOmDYEhHpQEpNTZWRtVis+wzpxe2Q1x4Sy+TNshYDaRlilbyYNH805CcuFcu+Iy1DFbYZe8Rm77c4lWHrixi2Pke6ZTTkJy/12RzShq0PHrxS5v3AyzsYtr7GR49XfybNHw0smQp58jtik/ezHq8csyUi0gHDlohIBwxbIiIdMGyJSBfNQZFoDOsrlv0Gw5aI3Ko5uDdOzHkV+xf9Bwfu2IiDt32OigFTxW4+j2FLRG51asYfUZ40zfa4ITwRx695HXV9hmr6+TqGLRG5TU3saFQOmArJYrYXJQkAUJZynb3mBxi2ROQ2TaHRAADZYNQ2SPC78VuGLRG5TXB5rlhSyEBIaY5Y9WkMWyJym+CKXMQdWKU8sFhswwlBVXmIPbJO29nHMWyJyK0G7HwFA3b+FaGl2Qiszkfs4U8w/Mv7YGysFrv6NIYtEbld3IGPMPKzhRiz+kYkbXsBATVFYhefx7AlItIBw5aISAcMWyIiHTBsiYh0wLAlItIBw5aISAcMWyIiHTBsichljeHxqBgwFTWxo8QmagfDlohckpf2IA7cth7Hr3kdR29aiey5y9EUGiN2IycYtkTUrtKUdORPvA+AxVar7jsWZ6b9VtOPnGPYElG7ypLnALIMSPbIkCzNKB94hd9tldhZDFsialdzULiyL6KKbDABACyBoZo6tY5hS0TtCs/L0pzVAoBksSCgthjBF05p6tQ6hi0Rtavf/pUILj+jqckGA/rvfFVTI+cYtkTULlN9OUZ8thCJu5ei9+nNiD20FiO+uAdRJ74Ru5ITDFsicomxqQb99i3D0G9+jaTtLyKs8GexC7XBY8PWYgqGOShcLBMReSWPC9vm4D44NeNZ7LtnG35atBk56W+jJna02I2IyKt4XNgen/MqyoZdA8ncBMliRlV8KnKu/weaQmPFrkREXsOjwrYqIQ01cWMAALIxwHaveUtAKEqHXSP0JiLyHh4Vto1hcWLJpjE8QSwRka+QAdkoidWetTi1ez6spNTUVBlZizXfo0vSMsSKy2r6jsXRucvFMgBgwPaXEHfoY7HcJinzfuDlHZDXHhKbyJPdMwF4+GLbQ6m2CfJHB4DyekgVDZCfnQE8+W9IkUFAZDDk2UOB5Ch7/x1ngb9nQj5WaquRZ5PmjwaWTIU8+R2xqedkLYY06V3IFvt+EJ2StRhIy1CF7QMbxC4dIwF46/ouhS0AnJz1Ii4MuRKSbIFsXbESVHEWo9bdBkNzg9i9bVmLgRe2AZ8cFlvI06QlAM9fCfQJATLPA+/vB348J/ZSWA/eVkUEAf81HlgwBggwQlq5H/LrP4q9yMP4Q9jahxH25HXpQ9pboPn7O+PCkFkILT6EPqf+DVNtKYwNFYjJ/hIpGx7seNACkCwyJMnD3pqQ1n0TlYPxreuBf2QpIfrwRudB257KBuD1H4Ep7wGzP4Q8dYDypPligdiTSFceMWbbFBqLw7eswclZL+D85EdxYfAsBFYXYMzqmzBwyx8RWFMofgl5OWnjHUrIrj6oBGxaBvDpEbFb15TWArd9AqRlQJ67Cth6t/I9R3APVtKfR4Ttucm/RF2foZpaTd+xyJv0iKZG3k8KMCqBV1itBGx1o9jFfaYth7R4A/DhPGDuCLGVyK08ImwvJM+BZGkSyyhNniOWyJtNHQB5572QZq6EfM8XYqsu5L15Ssj//nLgqzvEZiK36fmwlQyQJUncKtOqa+OtskECgpQ9N6lnScvmAq9fA8xfC7myXmzWX1oGEGg9y6aetzvP86Z+AV2/OKbS82ErW9DnxLeQjQFiC6JOfiuWOkz+78nA5kVimfS0417g+W1KwJ28ILb2nFkrlZ8pazGkUc7neJObbV4Eee0tYtUjSIbui8ju+5u6oH/mGwiq0F59Di09hoTMNzW1TsnYA0gSpPThYgvpIWsxUFTj2XNe7/oM8sobeYz0ACl9OCBJyvPUx3lE2AZW5WH0xzdj0PfPIH7POxi8+f8wct0CBNR10xN0+grIT18BpHIVmq6yFkPKrQBuXC22eJbDxcC8NZCfvgLSxYliK7lLaoLyvJy+QmzxSR4RtgAgyWZE52xAwp63EXXsK7G569IygLevh/TRzWILuUPWYuWM8eY1YotnOlOhTBF781ogKkRspe725QLg7a4vgvImHhO2ukjLgJwSLVapu71+jTJGe7hYbPF8k94BvlkoVqm7JYT7VdDC78IWgDTjfV4wc6dRscDUAcA6710iLVU08Bhxp82LlOehn/G7sJWrGiAdK+OUH3dITQBW3uT1Zyzyle8Dh4qVWRQEACgZcSMO/2I19t29BTnXZ6AqfqLYxTVZiyEdK4Nc1fHl997O78IWAOTF64GWK6HUfd6+HniwixsaeYpHvlLm4RIKx96B3Mt/h7qoZFgCwlCVOBE56Rmo7nuR2LVNLc+3luefv/HLsAUAPLBBuRJK3UZqMANZeWLZe937JfDkZWLVv0gS8i5+CAazalm1dQFS0ZiObe4jP31F13cX9GL+G7Z7fCgUPMGH83xvCs/+AuCWUWLVrzT0SoDFFAyLMVBsQm1MJ94Z+vHzziCpdhJ3l/wJ9+Lnu77B3vt/xLHr3kRNB99+uI119RB10YgYYEQM5Caz2OL9vjoG7PTfsduA2hLlE9lx2WpwxVmx5FxbexD7g4RwGGQ3h+3ZKY8j7+KH0BwUCVkyojJxMrJveBf1fYaIXclbfTgP0rJ9YtU3/N9mIMAImPzzTaDB3IB+Py0HJAMka+BKFuVFNfbIJ0Jvciq+FwzufLVpCotD0djbAQCyZL/YIEsGFI+cp+rZg/KrIL2dLlapg+Slu8WSz5CKapS7SPipxMw3Eb/3XUjWcduAmiIM3vx7ROZuFbu2Sno7HcivEsv+ZU++e8dsG8LjxZJCllHfZwhkg+PmM7pLXwU51cnPSe37diGw6bhY9Snytf8EZgwWy34lIestTFh2GcatnIWxq9IRdexrsYtTcmo8kL5KLPsdt4ZtYHVh67skShKq4idi7307kd2JKSTuIN0+ViyRK/qEAE9/L1bJR5nqy8VSm/i8snNz2BYg9tA6AIBkabSN9UCyDytUxytz9uojk9Rfqq+MPZAfnyJWyVVmx4snvkbaeEwskQvkx6dA+utOseyX3Bq2AJC07Xn0+2kFDOZmyAbruK2snN22kA0mlI640f5Feuuu7d0kAyqSpqEs+RrU9/GPt51Sow/OQGjN23u4CKaT5I8OiCW/5PawBYDEzDcwfvnlGLrpMbHJpkfPbK2khAix5LKa2NE4eOvnOD7nVZya+SwO3bIWeWkPit18S1wY5F93fYN3byDnVUL+rZ8vcOigrjyffJEuYdsiuCJXLNkEl58SS7qTrx8mllx2auZzaIhQ7ZcrW5A/8T5cGDxT3c2nSJclATs7MNfS23H5bod05fnki3QO2zOIOfIZAFjn7Cnr/iRzA2KOfC701tmGHEjTB4lVl9TEjkZD5ABtUVJ+teWDZ2jrvuSyJMDS6s3jiJTn04Ycsey3dA1bAAiuPANY59oCEiABQTWFCKwpELvqa31Op/e6lU2Brc+6AGAxBoslnyFf1vNDP+S55JRoYD3DtoVbwrY5JArNwX3EMppDonBu8q+0RRmoj0jq8KYWniS06DAMTQ322RYq4Xm+O9kfBievMETkoFvDtq4sCkfnLsP+hd9g/8JvkX3DO5qr8rVRyZr+aj2+X0IXNsgwmBswcOufIBu1Y3qRZ3cg7tDHmhqRX+nC88rXdFvYWgJCcHzTHHtoSkB1vwk4cfUrtjm1xsZq7RepGDs4WdrTRB37CiPXLUS/fcsRe2QdBn3/NJK/flTsBgBoDu6N85N+iey5y3Bi9l9xYehVYhfyUFJ4kFgickm3hW3Z4FlorO4lllEfmYQLQ2YBAMKKDyOsuPXbpUSd+EYs6auT47VqoSVHkLj7TSRtfR7RORvFZgCAOSgc2TcuR8H4RaiJG43ygZfj5JXPo2DcXWJX8kD+eIeBLumG55WnqokdhaIxC1Aych4ae/UTmx10W9g2hcWJJZumXva2wd/9DmGFB22PJYsZSVv/jPC8LFutR+h0xlI05jbUhyszF1rO+CXZjPOTH0VzcG+hN5GX0+l5pbe8tAdx9KaVODt1CXKnPYUDt2/AhSFtv0PttrBta55s8AV7W1DFGYz44r8wct3tGP7lfRj//gzEHvlU078nSAnhYsktauLG2Ka8tWgJ3Tov23ZSqmkSS0Ra4Y6bjnu7ygFTkD/xPs0ev5LFjFMznoU5yPlCjm4L2z6nvkN4fD5gnUPbsvdlxNldiDyzTegNhJbmoFfBTzA01YpNPSM9RZc5gabaUs1SZVj/owDA1FCpqXs6+YujYonIbkOOT25EU9Hfuo+KdS49AMgGI2Sjqc0bYXZb2AJA8rVfod/+lQisPIegynPot28ZkjcJU708lDwxXpc5gdHHNwHWoYMWssGIiLM7EFLmZVsVbjsDaZjvjslRF63PUZ5XvkYVshpyG23dHbYGoxmJP76OMWvmYfSaeUjcvVQTKh5Ph2kq4eczMfCHZyGZm+21/CwM2vJHTT+vkHke8ozOrbrzSsfLxAq1RYfnU0+IOJ+pfKJ6gyrJZkACehX8ZC8KujVsvZbOV0xjjn6B8SuuwMhPF2LMmpuQsv5B+72evI2bb6vkMeaOgPTwV2KVXKHz88vdInN/QN8D/7SeySo1WTJi0PfPwFTn/AWZYQtAemY6pC3ON8lpS3W/cThx1Us4sGA9cq5b6vLGM5KlGaElRxDUkZvmUc+5dwLkMg+5vuBFpC25kJ6ZLpa9Xv+dryJlw0NI2P0W+v/4GkavnY/onLZv086wbVnD/UrHNziujp+A7BveQ/ngmWgKi0VV4iScvOollA73r3uaSZP6iyXfo9NsFZ/zys5O7zni6cLzdiN+77vou/8DBF84KTY78PuwbblaKud1fCZA4UULbZ/LBpPt8/NpD9s+93XSTWsgL71WLPsU6aGL/WeT9G7W8rzixusMW+V2OP/TudVrNXFjNBe6WjSFxaIpJEos+yT5bAUAQIoKFZt8hnzvBOA3/xHL5CLpD1sgP32FWPY7BmQtFmv+5/vTYsUlAVX5gEH7eiXBAoOlCQH1FzR1XyZtyYX8+a1i2SdIAyIBAPIPnTtGCJDXZ4sl/5MaDwPSMsSy35DCg7q0kCHu0BrrvrxWsgUyDOi7fyUg+8+m2vKSfwGhHnBbejeQ182HxHtodd2GHP/exGdPvn8PI8ibFwHPdP423NHHvsKA7S/B0LKbmWRAv5+WI2H3P8Suvu+BDcC9zlfPeCtJBmTeHbbrnvleeb75Mb8NW+mjm4H8KrHcYXGHPsaEFdMxdtUNmPDeVCRmvil28Q978oCH0sSqV5O+XAD58uVimTorv0p53vkpvwxbKSFCmY6Svkps6rTAqjwYzI1i2a9IuRXAv31kq8iEcMgJ4UCD4wVQ6qT0VZBTov12OMEvw1b+8jb481i1u8g3rwHqmiDtuFds8irS1CTgywXApHfEJuqqtAy/HU7wv7B9enqnp3qRC9JXQfbyW37Lr8+BdPcXvHOwu/zPN8rz0M/4VdhK6cOVrRQ7OdWLXCNNXQbs9M6zWyl9OKTM85APFIpN1F2+Pw2kp/jdQgf/CdvNiyAvmcLhAx3Ijc3AQxuBrMWQYsPEZs+17R7Ij18C+eHWb2lE3SgtQ3k++tGQgn+EbUq0cnuO6SvEFnKXnwqAV3dB/voOoK/jvek8jfTdIkiBRmDG+2ITucv0Fcrz0kf3ThD5fNhK0wcBH93MM9qe8M+fgZe2AxtvF1s8y677IIcGQOYFMf2lZQAf3aw8T32cz4etnBIN6YbVYpn08vEh4JGvIGXeL7Z4BOm304CqBuCSd8Um0ol0w2qf3RlMzbfD1iJDenF7p3b0om606xxw2XIgazHgIdPCpF9OVn6eklrgqg/EZtKRnFcJ6aXtkOz3T/RJPh222tsqUk+SG5uVt4wF1cC2ewBDD/7vLJkKedE4YPaHkN/ZI7ZST/Hx/UR8OmzJA81bA1yoAzLvh/TUNLHVraTYMOVsdsEYJfhLeecF0g/DlvSXvkoJu8+zlfDbdZ9tK0N3kF6ZDWQthvzwxcr35cVS6gEMW+ox8uEiJfg25ED+7FYleOeNFLt1Tpz1LDZrMZCWAOmqD4A/dH6HN6KuklJTU2XlgOzaq71kMEDOvK/Lf093kjLvB17eAXntIbGJPJAUHw55/QJ7YfVB4LtTwN58dTdrgGqPMyk+HJiWBPmJS+21V3ZCXsW9aL2BNH+0MpY+2YOm33XnjRXSMuxhK4kHdCfIE+MdngQ9Kmsx8MI24JPDYgt5uogg4K+zgfH9xBbnSmqV/Yl3nRNbyNP9YhTwm8s8Kz9SE8RK57x9vTZsPeof2U14ZuujfPR49WceeWbbXazHK8dsiYh0wLAlItIBw5aISAcMWyIiHTBsiYh0wLAlItIBw5aISAcMWyIiHTBsiYh0wLAlItIBw5aISAcMWyIiHTBsiYh0wLAlItIBw5aISAcMWyIiHTBsiYh0wLAlItIBw5aISAcMWyIiHTBsiYh0wLAlItIBw5aISAcMW2pXUp96TBpUJZY75JLBlbhkcKVY7pBAk4yhMXUYV3ICA/o0IDTQInYh8lhSamqqjKzFQFqG2Ob1pMz7gZd3QF57SGwiF901uRCPTj8HADhWFII/fDUIRwtDxW5OTRhQjSevOoPk2DoAwBc/x+DZrweK3dp0/6X5uGRwJcYmVMMgadtOlIRg58kIbD8Zid254dpG8hrS/NHAkqmQJ78jNnk/a77yzJacGtWvxha0ADAsrg4v3ngSg6LrNf3a8tiMs7agBYC5F5VgwoBqTZ+2PH7lOTxwWR7GJToGLQAMjanDnZMK8Y/bcrDszmzMn1gEo0EWuxH1OIYtOTU2sUYsIbF3A35z9Rmx3Kp7phRgVHytWMb0YeViqVXTh5Xj9rRCsezURYnVeOKqs1j/4AHcNK5EbO6QUf0c/+1EXcGwJadG9nMMSgBIS6rCo9PPi2WNhMgG3Ds1XywDAIbE2M9025I+tlTz+FhRCL74OQarh83EpsNR2HOm9WGDuPAm/O+cXNw9pUBsatfci0qw+Vc/YeWio1h192H0790gdmnV7JFl+PMNJ7EgrUhsIgIYttQW9dldk1n7Hv6uyQVtDgfcf2k+gkz2C1hFVQG2zxMiG22ft2VAH/twRXF1AO75cASe/Xog/jL+Vvxu/WA8sCoF6W+Nxd8290d2K+PI4s/QnsuTy/H7a3IRHmwGrMMmT7pwFn95cjn+dMMpXD3yApZceRbPpZ8SuxAxbKl1sb2aMCTGHnYH8nphw8FoTZ97prR+5np5crnDWWl5nT1se4c0a9qcMaqOzmazhLomx8M1vyIQH2b2xR0rRuLxdUNxMC/M1hZotGD2yDJN/7ZcP9ax75TBlZg8qO1ZFNeO1n7dnFFlTn835L8cj14iAOP7a89ajxaG4o0tiaisN9lqUwZXYt54x7FR8e37B5l9YVadYBok1y5gmVQXuixyK1fHBD8c740Vu/ppaklRrg0DpMTVYWbKBbEMtDPGHGiSMXO449fdO7UAUWGuvaiQf2DYUqsGq85qAeBQXihKqgPw3g5tmN19ifatevrYUoxNsA8/nC8PwhtbEjVhaXDxqDMZ7WHbbGk/bAGgV5AyBNCirMb+4tCWacnOA/Xigc7nGF+cVNnqLIkgkwXpYxxfiMh/uXjYk7+JCWvSPD57IQgA8M/dffHTuV62enxkI/7fFXm2xzcKswCW7+oHs0WCrDqZNXbizFZ9ZtwW8Wzygmr4oi3ThlZoHmepLr4Niq5HvJNx5nHCOwC1yYOdh3SLOaPKcNfkQtwwlsHs6+yLGnzVC9uATw6LVWrH335xHJepAmjW6+NQXqecJU4dUoHXbzmu6g2kvzUWI/vW4KWbTtpqx4tDcNuyUQCA9+7MxrhEJZgazQZM/csEWz9ntj6+DyEBSsoeyg/DopUjlIY2FuE8cdUZzJ9YbHv88OphyMyN0PQRBZpk7Fiy1/Y4uzAUmbnhWDjJPu1syadDseVYb9vjFktvzdGsrjtdGqyZh3z1G+NaPbsek1CDx2eew0XW3wkA/GnTQHy2P0bTz2/8YhTwm8vEqu9Iy/DtFWTUeR/dfRgpccoUrap6I2a8Nl7T/rs5uZqz2FVZcRgcXa9ZkvuXfw/A6j1xAIB378i2jQM3mSVM+ctEW7/WhARYsPXxfbbHu05F4JGPhykP2jheP7nvkCbsZr42HpX1Rk0f0aSBlVh62zHb48/3x+Dn82H4v2tzbbWlPyRi2U7tEAoAbHt8H4KtLwi5ZcHYdSoCt6bap389t2kgPhcC9NbUIiy58qzD8MP+871w74fDtUXyflxBRm3pF2F/21xYFahpA4D3dsZrHk8fVq4J2vyKQFvQAoBZNebqygqvPqHaYQz1hTlnUuJqNUGbeTq83aAFgBHCfOKcolAcLw7R1AZFO84NHtWvxha0sF5E3HlKexY9aaB2JsNTs3Px61mOQQsA4xKrEaAapybfwrAlBxHBzYiwzjWFk7DNrwjE1uORtsfimOZn+2M1j9UR0lrQiMTpYa6EprjRzZ6zrS96ECXHai8GHikIxZHCMM0LxOBWliiLiz5yCkOw7UQkKqzDLQBw6VD7z/TU7FyH2RvidDaGre9i2JIDcdWUekGC2vetjGHCeha6Kst+VgsAFuECV3vTvyJDtLMKqlwKW+0FqR9Ptz1W2yI51h6aZouEA3lhkGUgp8h+dtsypKKW0ldbyy5SFlbsOGn/vmGBZlwxrBxPzT7jELSZp8Ox18UXBPJ+DFtyoB5CAIBiJ2GrvmKv9ulPMQ5nbOI8WfWChdZECbMhWi7OORMV2qR5y366NFizwMGZkACLJkiPFNhXop0qDbZ9bjTIDvs8pMRpHx84r3w/8YLcJYMqMW+8/aIdAKw/EI2H16QgLND+olLXZEBtYzu/GPJa/J8lB30jtEFXXO04jADrHNqGZu0hlF8RiIztCZpaa6R2hhKihSlcZbWtB34LMQh3uXhWOypeu+HMMdVYbW6ZPWwBYFCUdihBPdRSVBWImkbl7FuctXCLanYErEH7h68GAQBietl/166MS5P3YtiSg0hhvNTZMAKsgau2dGsiGpsdk1QcNmjWjhI46B2iDfzS6raDKC1JO4SwU/VWvi3DhaGAE22FrTBuq54HrN47orLeqBnPVlMHLayb5rQoqXb+eybvx7AlB6EB2iRsOWNrzXZVqG07EYmvD0Vp2luohw0ssuOwgqhPqDbwS2raDqJEYZz5ZKl2NoEzQ4UdyFrGXQHgZIk2bNUb40C4mCVu1PP5z47zZX88HYHnNtk3To8Ka0ag0T6YXdrOv5G8G8OWHIi3m6lucB62r23uj1e/Uz7++5NksdlGPd2r2dL+YSeuBCtqZUaE2kDVW/zKeiPyK9ru30IM20P59nHekyUhaDTbf9aBwj4LJoP99yQuJ95yrDcytsUjvyIQZbUB+HhvHB5bl6yZ4SCOjZe0c/ZO3q39o578Tpiwv0BbYQvrEt5/7u4rljU6uvQ2SjXPtqbR2O7PoN628Yzw9t+ZQdH1mrHeqnojFk0uwIyUcttUthPF9r9LHEZo68wWADK2JyD9rbG4+u8X4aVvBzgMr8SEacNWvTMa+R6GLTkQz2xdmePaHvWYbXMrwSRSz7Ntb7wWAMyqYYn2Lr61eGhanubnCg8244HL8vDyTSew/sEDWP/gAQQH2NsDjRbNLX4CTeqzdRe/qYp4EZBjtr6NYUsO1NORzBYJtW2M2brKpPor1MHoClfCUz2PV9IsoXBO3CFMFB/ZiMHCyrEk1bit9gJZx59K6pkI4DCCz+v4EUI+L1QVtu29fXeVesxWPW7pjGtxaae+4NbeHN4W6iECV6lXykntLMxoj7gkuaTGtXFm8k4uHpbkT8JUwwjdFraqYHIlbNVcOrNV5Z6rIShuLP7o2mF4ZuMgfJDZF9tPtj51K7G3PWzVF/rUZ7muEmdcFHMYwacxbH3Y7RcX4aUbT+D319h3r3KF+u11W9O+OkI7G0HT1Cq5g0MNnTmzVc8nrm8yYMfJCGw4GI3XNvfHr9Ym4673R2CNajMdAOgXYQ9o9UUx9UbnrlIvioCLY9PkvVw8LMmb3DiuBBsfPoDHZ57FzOHlmHtRCR6beU7s1qphcXWaECqs7J6zLfXmMx0NUldozmxdHIRQn223NpvgcEEYXv73AM0FQvWm6uoLfa5uiK4WHmT/Pdc0GjXTzMj38H/XhyRENuCVeSfwuzm56BuunVbU3sWgFhOEOw8cVM077Qr1YgH1565wjEFHnTmzdfWiXb1qnwf1TA31DITOnNmqN9spr+VZra9z8bAkT3fdmFKsWHgUV7Ryc8JD+WFYt89xRVNrxM1Vfj5vvwVOV7zwTRK+y+6N77J744VvksRmB+pNYNSfO6OejSAuDXZGO/fXediqZxqo59aqv6YzY7bqvXDrhT0myPfwf9gHPHHVWfzhutMOq652nYrAkk+HYtHKEThc4NoZ6vC+2rDd301hW1ZjwhOfD8UTnw9t9TYxoqU/JOBAXhgO5IVh6Q/tb2yj3uz7lItLdbXjyG2Frb3N2UKGzoStenGHq0Mf5L0Ytl7s+jGlWLnoKOZPtN+GpcWbPyTikY+HOexA1Z6qBnsQbj0e6bDqSS85RaG4+4MRuPuDEchxYdjh71sSsedMOPacCcfr3yeKza1SB2RbCy20oWpPyNOqlWotN8TsCFk1QOLq0Ad5L/4Xe6E5o8qw7M5sPHPdaYzqp90i8HB+KB5YlYLlrdwvyxVvbU1ATlEoDheE4Z3t2lvfeLKTJSF4YFUKHliVgtMuDDtACMi2hiqcheI72+NxpCAU2YWhLm0rKVKf2bo69EHei2HrRWaNuICM23PwXPopzV1ZW6zdG4u7Vo7EHiebervi5/NhuH35SNz1vutDD97qrW0JOFKgvLBkbHP+wpJbZg/lEyX2IYqDeWFY+P5I3LFiJH62bhzeEeqLeq7cKoi8G8PWw8WFN+LW1CKsWHgUL8w9iYkDtPu2AsrtW57ZOAgvftv+hSeyawnL9l5Y3t6WgD1nwnEwLwxvbHFtiMIVR1V3hcgudG2cmbwXb2XuoVLi6vDEVWdst/9uzcmSYKzdF4e1e7U3V+xJBkmGySAjwCjDaJBhkJTbvYh3dOgSHzleI4LN+O1sZcHJ8/9K4p0afJX1eGXYeqhlC4/iogTteGyLZrOEygaTSzdB7G5GgwyjJMNktP9pMsgwGZWLR87eDltkoKHZgPomAxrNyp8NzRIam5UgVj4kNJkNKK8zobzWiPK6AJTVmlBWY0JZbQCKqgKUTXF4vJI3Ydh6tv/8aj8ig7VTuUhZaVUWFY0L2bW4UGvChVoTKupNqKhT9rxVPkyobjCist6Imlb2dpCt83KbLZL1w4AmswS5h65RGSTlnUCQSXnxgvUFtcksodEstTkHmLwAw9azvX/XUYwWbkZI7mW2hm9xdQAKKwNRXB1g/QhEYaXyZ1FVAAoqHXfnighuRkJkI/pGNCIuvAmxvZoQHdaEmF5NiO3ViGCTBSajEqomg4xAk/UdgUEZbmmLRVY2vTFblGlozWbl5zRbJJTWBOCFb5JwtLD96XHUQxi2nu2ixBo8NTtXs1m1WkWdqUduey1bz7panuwtf5plJQTMFmXpa7NZsl1tDzRZEGiUEWSy2D8ClMfBJotmJZU3sMhAYWUgggJkhASYEdLDP//2k5H41VrntySiHsaw9Q63TCzGLROKMUS4VxYA/G1zf3yY2fbtaLxFSIAFIYEWBJvMiOnVjKjQJvQJbUaf0Gb0DmlCb9vnzYgaEoSoqnLNai5/xrD1cAxb7zJ/YjHunFSgudcWALy3Ix7/2NrxCfVezXq8RoU1IyasCVFhTYgIbkavILPqw4LQQDOCTJZWN7KRJGUFWct4qcmozJwIMFrQN7wJccJGPl1RVa+MJTdblHHYZov1XYCsXBBsNivvBlqGCGDd2MZkUP40SspQQ8uQQ8ufAUYZFXUmDiN4Ooat9xkSU4fn0k87bBbz6U+x+PO//GiOrQ7Ha4BRRmLvBvSLaETfcGUctk9ok+2sO8AoIzjAgrpGZSZFXZMBxdUBKKtRZk2U1Chju/kVgZzS5e8Ytt4pKrQJz889hdQk7eKGrccj8fTGwd1yc0aPx+OVvIn1eNX/Cgt1SVltAB5e47jBzLTkCry1IBvjWlnGS0Q9j2HrhcwWCUs+HYpP9mlXjqXE1eG9O7Ox7v5D+PWss7h0SIWmnYh6DsPWi73wTVKre70OjKrHralFeO2W4/jhsX149ebjDrfNJiJ9MWy93LKd8Xhm4yBccHJbldBAC6YlV2DR5AKxiYh0xLD1ARsORuPWZaPxt839setUhNgMCNv5EZH+GLY+oqzGhA8z++KRj4fh6jfG4U+bBmLT4SjkFIXgP9l9vGojcCJfxLD1QWU1Jny2Pwa/Wz8Yty8fhSc/H4LqVjZkISL9MGyJiHTAsCUi0gHDlohIBwxbIiIdMGyJiHRg34iGiIjcw7brVyrnYBIRuc2efPx/YqTp9vg7FBgAAAAASUVORK5CYII=</t>
+  </si>
+  <si>
+    <t>ΜΑΡΝΕΡΗΣ</t>
   </si>
 </sst>
 </file>
@@ -2610,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="AS13" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AT13" s="1" t="s">
         <v>143</v>
@@ -2714,7 +2714,7 @@
         <v>0</v>
       </c>
       <c r="AS14" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AT14" s="1" t="s">
         <v>143</v>
@@ -2804,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="AS15" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AT15" s="1" t="s">
         <v>143</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="16" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>136</v>
@@ -2890,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="AS16" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AT16" s="1" t="s">
         <v>143</v>
@@ -2910,7 +2910,7 @@
     </row>
     <row r="17" spans="1:50" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>134</v>
@@ -2966,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="AS17" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AT17" s="1" t="s">
         <v>143</v>
@@ -3204,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="V2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="W2">
         <v>35</v>
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="V3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="W3">
         <v>35</v>
